--- a/Cronograma das Aulas.xlsx
+++ b/Cronograma das Aulas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ismaelcosta/Desktop/+praTI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBFF90A1-6C27-5145-8FB1-8ACEF2B8AEE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5E7B39-2B00-A847-9824-E462FA1CF5CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22400" yWindow="640" windowWidth="22420" windowHeight="23360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="44800" windowHeight="23360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cronograma" sheetId="1" r:id="rId1"/>
@@ -376,7 +376,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -462,12 +462,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -475,16 +469,77 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -804,21 +859,21 @@
   <cols>
     <col min="1" max="1" width="79" customWidth="1"/>
     <col min="2" max="2" width="21.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -832,7 +887,7 @@
       <c r="B3" s="7">
         <v>46141</v>
       </c>
-      <c r="C3" s="5" t="b">
+      <c r="C3" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -843,7 +898,7 @@
       <c r="B4" s="7">
         <v>46142</v>
       </c>
-      <c r="C4" s="5" t="b">
+      <c r="C4" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -854,7 +909,7 @@
       <c r="B5" s="7">
         <v>46146</v>
       </c>
-      <c r="C5" s="5" t="b">
+      <c r="C5" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -865,7 +920,7 @@
       <c r="B6" s="7">
         <v>46148</v>
       </c>
-      <c r="C6" s="5" t="b">
+      <c r="C6" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -876,7 +931,7 @@
       <c r="B7" s="7">
         <v>46149</v>
       </c>
-      <c r="C7" s="5" t="b">
+      <c r="C7" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -887,7 +942,7 @@
       <c r="B8" s="7">
         <v>46149</v>
       </c>
-      <c r="C8" s="5" t="b">
+      <c r="C8" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -898,7 +953,7 @@
       <c r="B9" s="7">
         <v>46153</v>
       </c>
-      <c r="C9" s="5" t="b">
+      <c r="C9" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -909,7 +964,7 @@
       <c r="B10" s="7">
         <v>46155</v>
       </c>
-      <c r="C10" s="5" t="b">
+      <c r="C10" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -920,7 +975,7 @@
       <c r="B11" s="7">
         <v>46156</v>
       </c>
-      <c r="C11" s="5" t="b">
+      <c r="C11" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -931,7 +986,7 @@
       <c r="B12" s="7">
         <v>46156</v>
       </c>
-      <c r="C12" s="5" t="b">
+      <c r="C12" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -942,7 +997,7 @@
       <c r="B13" s="7">
         <v>46160</v>
       </c>
-      <c r="C13" s="5" t="b">
+      <c r="C13" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -953,7 +1008,7 @@
       <c r="B14" s="7">
         <v>46162</v>
       </c>
-      <c r="C14" s="5" t="b">
+      <c r="C14" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -964,7 +1019,7 @@
       <c r="B15" s="7">
         <v>46163</v>
       </c>
-      <c r="C15" s="5" t="b">
+      <c r="C15" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -975,22 +1030,22 @@
       <c r="B16" s="7">
         <v>46163</v>
       </c>
-      <c r="C16" s="5" t="b">
+      <c r="C16" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -1004,7 +1059,7 @@
       <c r="B21" s="7">
         <v>46167</v>
       </c>
-      <c r="C21" s="5" t="b">
+      <c r="C21" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1013,7 +1068,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="7"/>
-      <c r="C22" s="5" t="b">
+      <c r="C22" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1022,7 +1077,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="7"/>
-      <c r="C23" s="5" t="b">
+      <c r="C23" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1031,7 +1086,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="7"/>
-      <c r="C24" s="5" t="b">
+      <c r="C24" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1040,7 +1095,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="7"/>
-      <c r="C25" s="5" t="b">
+      <c r="C25" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1049,7 +1104,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="7"/>
-      <c r="C26" s="5" t="b">
+      <c r="C26" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1058,7 +1113,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="7"/>
-      <c r="C27" s="5" t="b">
+      <c r="C27" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1067,7 +1122,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="7"/>
-      <c r="C28" s="5" t="b">
+      <c r="C28" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1076,7 +1131,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="7"/>
-      <c r="C29" s="5" t="b">
+      <c r="C29" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1085,7 +1140,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="7"/>
-      <c r="C30" s="5" t="b">
+      <c r="C30" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1094,7 +1149,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="7"/>
-      <c r="C31" s="5" t="b">
+      <c r="C31" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1103,7 +1158,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="7"/>
-      <c r="C32" s="5" t="b">
+      <c r="C32" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1112,7 +1167,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="7"/>
-      <c r="C33" s="5" t="b">
+      <c r="C33" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1121,7 +1176,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="7"/>
-      <c r="C34" s="5" t="b">
+      <c r="C34" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1130,22 +1185,22 @@
         <v>32</v>
       </c>
       <c r="B35" s="7"/>
-      <c r="C35" s="5" t="b">
+      <c r="C35" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -1157,7 +1212,7 @@
         <v>34</v>
       </c>
       <c r="B40" s="7"/>
-      <c r="C40" s="5" t="b">
+      <c r="C40" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1166,7 +1221,7 @@
         <v>35</v>
       </c>
       <c r="B41" s="7"/>
-      <c r="C41" s="5" t="b">
+      <c r="C41" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1175,7 +1230,7 @@
         <v>36</v>
       </c>
       <c r="B42" s="7"/>
-      <c r="C42" s="5" t="b">
+      <c r="C42" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1184,7 +1239,7 @@
         <v>37</v>
       </c>
       <c r="B43" s="7"/>
-      <c r="C43" s="5" t="b">
+      <c r="C43" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1193,7 +1248,7 @@
         <v>38</v>
       </c>
       <c r="B44" s="7"/>
-      <c r="C44" s="5" t="b">
+      <c r="C44" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1202,7 +1257,7 @@
         <v>39</v>
       </c>
       <c r="B45" s="7"/>
-      <c r="C45" s="5" t="b">
+      <c r="C45" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1211,7 +1266,7 @@
         <v>40</v>
       </c>
       <c r="B46" s="7"/>
-      <c r="C46" s="5" t="b">
+      <c r="C46" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1220,7 +1275,7 @@
         <v>41</v>
       </c>
       <c r="B47" s="7"/>
-      <c r="C47" s="5" t="b">
+      <c r="C47" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1229,7 +1284,7 @@
         <v>42</v>
       </c>
       <c r="B48" s="7"/>
-      <c r="C48" s="5" t="b">
+      <c r="C48" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1238,7 +1293,7 @@
         <v>43</v>
       </c>
       <c r="B49" s="7"/>
-      <c r="C49" s="5" t="b">
+      <c r="C49" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1247,7 +1302,7 @@
         <v>44</v>
       </c>
       <c r="B50" s="7"/>
-      <c r="C50" s="5" t="b">
+      <c r="C50" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1256,7 +1311,7 @@
         <v>45</v>
       </c>
       <c r="B51" s="7"/>
-      <c r="C51" s="5" t="b">
+      <c r="C51" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1265,7 +1320,7 @@
         <v>46</v>
       </c>
       <c r="B52" s="7"/>
-      <c r="C52" s="5" t="b">
+      <c r="C52" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1274,7 +1329,7 @@
         <v>47</v>
       </c>
       <c r="B53" s="7"/>
-      <c r="C53" s="5" t="b">
+      <c r="C53" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1283,7 +1338,7 @@
         <v>48</v>
       </c>
       <c r="B54" s="7"/>
-      <c r="C54" s="5" t="b">
+      <c r="C54" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1292,7 +1347,7 @@
         <v>49</v>
       </c>
       <c r="B55" s="7"/>
-      <c r="C55" s="5" t="b">
+      <c r="C55" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1301,22 +1356,22 @@
         <v>50</v>
       </c>
       <c r="B56" s="7"/>
-      <c r="C56" s="5" t="b">
+      <c r="C56" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="1" t="s">
@@ -1328,7 +1383,7 @@
         <v>55</v>
       </c>
       <c r="B61" s="7"/>
-      <c r="C61" s="5" t="b">
+      <c r="C61" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1337,7 +1392,7 @@
         <v>56</v>
       </c>
       <c r="B62" s="7"/>
-      <c r="C62" s="5" t="b">
+      <c r="C62" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1346,7 +1401,7 @@
         <v>57</v>
       </c>
       <c r="B63" s="7"/>
-      <c r="C63" s="5" t="b">
+      <c r="C63" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1355,7 +1410,7 @@
         <v>58</v>
       </c>
       <c r="B64" s="7"/>
-      <c r="C64" s="5" t="b">
+      <c r="C64" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1364,7 +1419,7 @@
         <v>59</v>
       </c>
       <c r="B65" s="7"/>
-      <c r="C65" s="5" t="b">
+      <c r="C65" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1373,7 +1428,7 @@
         <v>52</v>
       </c>
       <c r="B66" s="7"/>
-      <c r="C66" s="5" t="b">
+      <c r="C66" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1382,7 +1437,7 @@
         <v>60</v>
       </c>
       <c r="B67" s="7"/>
-      <c r="C67" s="5" t="b">
+      <c r="C67" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1391,7 +1446,7 @@
         <v>61</v>
       </c>
       <c r="B68" s="7"/>
-      <c r="C68" s="5" t="b">
+      <c r="C68" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1400,7 +1455,7 @@
         <v>62</v>
       </c>
       <c r="B69" s="7"/>
-      <c r="C69" s="5" t="b">
+      <c r="C69" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1409,7 +1464,7 @@
         <v>63</v>
       </c>
       <c r="B70" s="7"/>
-      <c r="C70" s="5" t="b">
+      <c r="C70" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1418,7 +1473,7 @@
         <v>64</v>
       </c>
       <c r="B71" s="7"/>
-      <c r="C71" s="5" t="b">
+      <c r="C71" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1427,7 +1482,7 @@
         <v>65</v>
       </c>
       <c r="B72" s="7"/>
-      <c r="C72" s="5" t="b">
+      <c r="C72" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1436,7 +1491,7 @@
         <v>66</v>
       </c>
       <c r="B73" s="7"/>
-      <c r="C73" s="5" t="b">
+      <c r="C73" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1445,7 +1500,7 @@
         <v>67</v>
       </c>
       <c r="B74" s="7"/>
-      <c r="C74" s="5" t="b">
+      <c r="C74" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1454,7 +1509,7 @@
         <v>68</v>
       </c>
       <c r="B75" s="7"/>
-      <c r="C75" s="5" t="b">
+      <c r="C75" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1463,7 +1518,7 @@
         <v>69</v>
       </c>
       <c r="B76" s="7"/>
-      <c r="C76" s="5" t="b">
+      <c r="C76" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1472,7 +1527,7 @@
         <v>70</v>
       </c>
       <c r="B77" s="7"/>
-      <c r="C77" s="5" t="b">
+      <c r="C77" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1481,7 +1536,7 @@
         <v>71</v>
       </c>
       <c r="B78" s="7"/>
-      <c r="C78" s="5" t="b">
+      <c r="C78" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1490,7 +1545,7 @@
         <v>72</v>
       </c>
       <c r="B79" s="7"/>
-      <c r="C79" s="5" t="b">
+      <c r="C79" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1499,22 +1554,22 @@
         <v>73</v>
       </c>
       <c r="B80" s="7"/>
-      <c r="C80" s="5" t="b">
+      <c r="C80" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="6"/>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B84" s="6" t="s">
+      <c r="B84" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C84" s="1" t="s">
@@ -1526,7 +1581,7 @@
         <v>74</v>
       </c>
       <c r="B85" s="7"/>
-      <c r="C85" s="5" t="b">
+      <c r="C85" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1535,7 +1590,7 @@
         <v>75</v>
       </c>
       <c r="B86" s="7"/>
-      <c r="C86" s="5" t="b">
+      <c r="C86" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1544,7 +1599,7 @@
         <v>76</v>
       </c>
       <c r="B87" s="7"/>
-      <c r="C87" s="5" t="b">
+      <c r="C87" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1553,7 +1608,7 @@
         <v>77</v>
       </c>
       <c r="B88" s="7"/>
-      <c r="C88" s="5" t="b">
+      <c r="C88" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1562,7 +1617,7 @@
         <v>78</v>
       </c>
       <c r="B89" s="7"/>
-      <c r="C89" s="5" t="b">
+      <c r="C89" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1571,7 +1626,7 @@
         <v>79</v>
       </c>
       <c r="B90" s="7"/>
-      <c r="C90" s="5" t="b">
+      <c r="C90" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1580,7 +1635,7 @@
         <v>80</v>
       </c>
       <c r="B91" s="7"/>
-      <c r="C91" s="5" t="b">
+      <c r="C91" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1589,7 +1644,7 @@
         <v>81</v>
       </c>
       <c r="B92" s="7"/>
-      <c r="C92" s="5" t="b">
+      <c r="C92" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1598,7 +1653,7 @@
         <v>82</v>
       </c>
       <c r="B93" s="7"/>
-      <c r="C93" s="5" t="b">
+      <c r="C93" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1607,7 +1662,7 @@
         <v>83</v>
       </c>
       <c r="B94" s="7"/>
-      <c r="C94" s="5" t="b">
+      <c r="C94" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1616,7 +1671,7 @@
         <v>84</v>
       </c>
       <c r="B95" s="7"/>
-      <c r="C95" s="5" t="b">
+      <c r="C95" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1625,7 +1680,7 @@
         <v>85</v>
       </c>
       <c r="B96" s="7"/>
-      <c r="C96" s="5" t="b">
+      <c r="C96" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1634,7 +1689,7 @@
         <v>86</v>
       </c>
       <c r="B97" s="7"/>
-      <c r="C97" s="5" t="b">
+      <c r="C97" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1643,7 +1698,7 @@
         <v>87</v>
       </c>
       <c r="B98" s="7"/>
-      <c r="C98" s="5" t="b">
+      <c r="C98" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1652,7 +1707,7 @@
         <v>88</v>
       </c>
       <c r="B99" s="7"/>
-      <c r="C99" s="5" t="b">
+      <c r="C99" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1661,7 +1716,7 @@
         <v>89</v>
       </c>
       <c r="B100" s="7"/>
-      <c r="C100" s="5" t="b">
+      <c r="C100" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1670,7 +1725,7 @@
         <v>90</v>
       </c>
       <c r="B101" s="7"/>
-      <c r="C101" s="5" t="b">
+      <c r="C101" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1679,7 +1734,7 @@
         <v>91</v>
       </c>
       <c r="B102" s="7"/>
-      <c r="C102" s="5" t="b">
+      <c r="C102" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1688,7 +1743,7 @@
         <v>92</v>
       </c>
       <c r="B103" s="7"/>
-      <c r="C103" s="5" t="b">
+      <c r="C103" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1697,22 +1752,22 @@
         <v>93</v>
       </c>
       <c r="B104" s="7"/>
-      <c r="C104" s="5" t="b">
+      <c r="C104" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="A107" s="3" t="s">
+      <c r="A107" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B107" s="3"/>
-      <c r="C107" s="3"/>
+      <c r="B107" s="6"/>
+      <c r="C107" s="6"/>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B108" s="6" t="s">
+      <c r="B108" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C108" s="1" t="s">
@@ -1724,7 +1779,7 @@
         <v>94</v>
       </c>
       <c r="B109" s="7"/>
-      <c r="C109" s="5" t="b">
+      <c r="C109" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1733,7 +1788,7 @@
         <v>95</v>
       </c>
       <c r="B110" s="7"/>
-      <c r="C110" s="5" t="b">
+      <c r="C110" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1742,7 +1797,7 @@
         <v>96</v>
       </c>
       <c r="B111" s="7"/>
-      <c r="C111" s="5" t="b">
+      <c r="C111" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1751,7 +1806,7 @@
         <v>97</v>
       </c>
       <c r="B112" s="7"/>
-      <c r="C112" s="5" t="b">
+      <c r="C112" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1760,7 +1815,7 @@
         <v>98</v>
       </c>
       <c r="B113" s="7"/>
-      <c r="C113" s="5" t="b">
+      <c r="C113" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1769,7 +1824,7 @@
         <v>99</v>
       </c>
       <c r="B114" s="7"/>
-      <c r="C114" s="5" t="b">
+      <c r="C114" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1778,7 +1833,7 @@
         <v>100</v>
       </c>
       <c r="B115" s="7"/>
-      <c r="C115" s="5" t="b">
+      <c r="C115" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1787,7 +1842,7 @@
         <v>101</v>
       </c>
       <c r="B116" s="7"/>
-      <c r="C116" s="5" t="b">
+      <c r="C116" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1796,7 +1851,7 @@
         <v>102</v>
       </c>
       <c r="B117" s="7"/>
-      <c r="C117" s="5" t="b">
+      <c r="C117" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1805,7 +1860,7 @@
         <v>103</v>
       </c>
       <c r="B118" s="7"/>
-      <c r="C118" s="5" t="b">
+      <c r="C118" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1814,7 +1869,7 @@
         <v>104</v>
       </c>
       <c r="B119" s="7"/>
-      <c r="C119" s="5" t="b">
+      <c r="C119" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1823,7 +1878,7 @@
         <v>105</v>
       </c>
       <c r="B120" s="7"/>
-      <c r="C120" s="5" t="b">
+      <c r="C120" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1832,7 +1887,7 @@
         <v>106</v>
       </c>
       <c r="B121" s="7"/>
-      <c r="C121" s="5" t="b">
+      <c r="C121" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1841,7 +1896,7 @@
         <v>107</v>
       </c>
       <c r="B122" s="7"/>
-      <c r="C122" s="5" t="b">
+      <c r="C122" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1850,7 +1905,7 @@
         <v>108</v>
       </c>
       <c r="B123" s="7"/>
-      <c r="C123" s="5" t="b">
+      <c r="C123" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1859,19 +1914,34 @@
         <v>109</v>
       </c>
       <c r="B124" s="7"/>
-      <c r="C124" s="5" t="b">
+      <c r="C124" s="3" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A107:C107"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A59:C59"/>
     <mergeCell ref="A83:C83"/>
-    <mergeCell ref="A107:C107"/>
   </mergeCells>
+  <conditionalFormatting sqref="C3:C16">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C21:C35 C40:C56 C61:C80 C85:C104 C109:C124">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:C16 C21:C35 C40:C56 C61:C80 C85:C104 C109:C124">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
